--- a/evaluation/results/Qualitative Evaluations - System 1, System 2 and System 3/Evaluation-Sheet-ver.xlsx
+++ b/evaluation/results/Qualitative Evaluations - System 1, System 2 and System 3/Evaluation-Sheet-ver.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSouzaJ\Datasets\subject-indexing-dataset\evaluation\results\Qualitative Evaluations - System 1, System 2 and System 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SadruddinS\Data\GermEval25\Qualitative Evaluations\Qualitative Evaluations-LA2I2F,DNB,ANNIF-updated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2457B3-91BE-4778-8420-34E5B750F20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="12000" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="LLMs4Subjects Evaluation Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -28,12 +24,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Arndt, Susanne</author>
   </authors>
   <commentList>
-    <comment ref="K115" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="K115" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1222,22 +1218,22 @@
     <t>Direkteinspritzung | gnd:4150126-3</t>
   </si>
   <si>
+    <t>LA2I2F - Team 1</t>
+  </si>
+  <si>
     <t>Code</t>
   </si>
   <si>
-    <t>System 1</t>
-  </si>
-  <si>
-    <t>System 2</t>
-  </si>
-  <si>
-    <t>System 3</t>
+    <t>DNB-AI - Team 2</t>
+  </si>
+  <si>
+    <t>Annif - Team 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1376,19 +1372,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle1" displayName="Tabelle1" ref="A1:K201" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:K201" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Record ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Title"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Language"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Subject Classification"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="System 1"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Code"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="System 2"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Code2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="System 3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Code3"/>
+    <tableColumn id="1" name="Record ID"/>
+    <tableColumn id="2" name="Title"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Language"/>
+    <tableColumn id="5" name="Subject Classification"/>
+    <tableColumn id="11" name="LA2I2F - Team 1"/>
+    <tableColumn id="12" name="Code"/>
+    <tableColumn id="10" name="DNB-AI - Team 2"/>
+    <tableColumn id="13" name="Code2"/>
+    <tableColumn id="7" name="Annif - Team 3"/>
+    <tableColumn id="8" name="Code3"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1572,7 +1568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K201"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1606,10 +1602,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>388</v>
@@ -1641,10 +1637,10 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>248</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
@@ -1676,10 +1672,10 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>249</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1711,10 +1707,10 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>250</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
@@ -1746,10 +1742,10 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>251</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J5" t="s">
         <v>18</v>
@@ -1775,10 +1771,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>252</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
@@ -1804,10 +1800,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s">
         <v>19</v>
@@ -1833,7 +1829,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="G8" t="s">
         <v>49</v>
@@ -1862,7 +1858,7 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>258</v>
       </c>
       <c r="G9" t="s">
         <v>49</v>
@@ -1949,7 +1945,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>175</v>
+        <v>253</v>
       </c>
       <c r="G12" t="s">
         <v>49</v>
@@ -1978,7 +1974,7 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G13" t="s">
         <v>49</v>
@@ -2007,10 +2003,10 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s">
         <v>27</v>
@@ -2036,10 +2032,10 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>249</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J15" t="s">
         <v>28</v>
@@ -2065,10 +2061,10 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>256</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J16" t="s">
         <v>29</v>
@@ -2094,10 +2090,10 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>248</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J17" t="s">
         <v>30</v>
@@ -2123,7 +2119,7 @@
         <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G18" t="s">
         <v>49</v>
@@ -2152,7 +2148,7 @@
         <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>258</v>
+        <v>25</v>
       </c>
       <c r="G19" t="s">
         <v>49</v>
@@ -2181,10 +2177,10 @@
         <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J20" t="s">
         <v>33</v>
@@ -2210,10 +2206,10 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>257</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J21" t="s">
         <v>35</v>
@@ -2239,10 +2235,10 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>259</v>
+        <v>203</v>
       </c>
       <c r="G22" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s">
         <v>38</v>
@@ -2274,10 +2270,10 @@
         <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>260</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H23" t="s">
         <v>40</v>
@@ -2309,10 +2305,10 @@
         <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G24" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s">
         <v>39</v>
@@ -2344,7 +2340,7 @@
         <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G25" t="s">
         <v>49</v>
@@ -2379,7 +2375,7 @@
         <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G26" t="s">
         <v>49</v>
@@ -2437,7 +2433,7 @@
         <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>262</v>
       </c>
       <c r="G28" t="s">
         <v>49</v>
@@ -2466,10 +2462,10 @@
         <v>11</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>273</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J29" t="s">
         <v>44</v>
@@ -2495,10 +2491,10 @@
         <v>11</v>
       </c>
       <c r="F30" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J30" t="s">
         <v>48</v>
@@ -2524,7 +2520,7 @@
         <v>11</v>
       </c>
       <c r="F31" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
@@ -2553,7 +2549,7 @@
         <v>11</v>
       </c>
       <c r="F32" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="G32" t="s">
         <v>16</v>
@@ -2582,10 +2578,10 @@
         <v>11</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>263</v>
       </c>
       <c r="G33" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J33" t="s">
         <v>52</v>
@@ -2640,10 +2636,10 @@
         <v>11</v>
       </c>
       <c r="F35" t="s">
-        <v>267</v>
+        <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J35" t="s">
         <v>54</v>
@@ -2669,7 +2665,7 @@
         <v>11</v>
       </c>
       <c r="F36" t="s">
-        <v>268</v>
+        <v>51</v>
       </c>
       <c r="G36" t="s">
         <v>16</v>
@@ -2756,7 +2752,7 @@
         <v>11</v>
       </c>
       <c r="F39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G39" t="s">
         <v>16</v>
@@ -2785,7 +2781,7 @@
         <v>11</v>
       </c>
       <c r="F40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G40" t="s">
         <v>16</v>
@@ -2814,10 +2810,10 @@
         <v>11</v>
       </c>
       <c r="F41" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G41" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J41" t="s">
         <v>59</v>
@@ -2843,7 +2839,7 @@
         <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>274</v>
+        <v>71</v>
       </c>
       <c r="G42" t="s">
         <v>49</v>
@@ -2878,10 +2874,10 @@
         <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>275</v>
+        <v>66</v>
       </c>
       <c r="G43" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H43" t="s">
         <v>66</v>
@@ -2913,10 +2909,10 @@
         <v>63</v>
       </c>
       <c r="F44" t="s">
-        <v>276</v>
+        <v>64</v>
       </c>
       <c r="G44" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H44" t="s">
         <v>68</v>
@@ -2948,7 +2944,7 @@
         <v>63</v>
       </c>
       <c r="F45" t="s">
-        <v>74</v>
+        <v>279</v>
       </c>
       <c r="G45" t="s">
         <v>49</v>
@@ -2983,10 +2979,10 @@
         <v>63</v>
       </c>
       <c r="F46" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G46" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J46" t="s">
         <v>70</v>
@@ -3012,7 +3008,7 @@
         <v>63</v>
       </c>
       <c r="F47" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G47" t="s">
         <v>49</v>
@@ -3041,7 +3037,7 @@
         <v>63</v>
       </c>
       <c r="F48" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="G48" t="s">
         <v>49</v>
@@ -3070,10 +3066,10 @@
         <v>63</v>
       </c>
       <c r="F49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J49" t="s">
         <v>73</v>
@@ -3099,7 +3095,7 @@
         <v>63</v>
       </c>
       <c r="F50" t="s">
-        <v>278</v>
+        <v>73</v>
       </c>
       <c r="G50" t="s">
         <v>49</v>
@@ -3128,7 +3124,7 @@
         <v>63</v>
       </c>
       <c r="F51" t="s">
-        <v>81</v>
+        <v>275</v>
       </c>
       <c r="G51" t="s">
         <v>49</v>
@@ -3157,10 +3153,10 @@
         <v>63</v>
       </c>
       <c r="F52" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G52" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J52" t="s">
         <v>77</v>
@@ -3186,7 +3182,7 @@
         <v>63</v>
       </c>
       <c r="F53" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G53" t="s">
         <v>49</v>
@@ -3215,7 +3211,7 @@
         <v>63</v>
       </c>
       <c r="F54" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G54" t="s">
         <v>49</v>
@@ -3244,10 +3240,10 @@
         <v>63</v>
       </c>
       <c r="F55" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G55" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J55" t="s">
         <v>82</v>
@@ -3273,10 +3269,10 @@
         <v>63</v>
       </c>
       <c r="F56" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J56" t="s">
         <v>83</v>
@@ -3302,10 +3298,10 @@
         <v>63</v>
       </c>
       <c r="F57" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="G57" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J57" t="s">
         <v>84</v>
@@ -3331,10 +3327,10 @@
         <v>63</v>
       </c>
       <c r="F58" t="s">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="G58" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J58" t="s">
         <v>85</v>
@@ -3360,10 +3356,10 @@
         <v>63</v>
       </c>
       <c r="F59" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J59" t="s">
         <v>78</v>
@@ -3389,7 +3385,7 @@
         <v>63</v>
       </c>
       <c r="F60" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s">
         <v>49</v>
@@ -3418,7 +3414,7 @@
         <v>63</v>
       </c>
       <c r="F61" t="s">
-        <v>70</v>
+        <v>276</v>
       </c>
       <c r="G61" t="s">
         <v>49</v>
@@ -3447,10 +3443,10 @@
         <v>90</v>
       </c>
       <c r="F62" t="s">
-        <v>280</v>
+        <v>91</v>
       </c>
       <c r="G62" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H62" t="s">
         <v>92</v>
@@ -3482,7 +3478,7 @@
         <v>90</v>
       </c>
       <c r="F63" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="G63" t="s">
         <v>49</v>
@@ -3517,7 +3513,7 @@
         <v>90</v>
       </c>
       <c r="F64" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="G64" t="s">
         <v>49</v>
@@ -3546,7 +3542,7 @@
         <v>90</v>
       </c>
       <c r="F65" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="G65" t="s">
         <v>49</v>
@@ -3575,7 +3571,7 @@
         <v>90</v>
       </c>
       <c r="F66" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G66" t="s">
         <v>49</v>
@@ -3604,7 +3600,7 @@
         <v>90</v>
       </c>
       <c r="F67" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="G67" t="s">
         <v>49</v>
@@ -3633,7 +3629,7 @@
         <v>90</v>
       </c>
       <c r="F68" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G68" t="s">
         <v>49</v>
@@ -3662,7 +3658,7 @@
         <v>90</v>
       </c>
       <c r="F69" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="G69" t="s">
         <v>49</v>
@@ -3691,7 +3687,7 @@
         <v>90</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>287</v>
       </c>
       <c r="G70" t="s">
         <v>49</v>
@@ -3720,7 +3716,7 @@
         <v>90</v>
       </c>
       <c r="F71" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="G71" t="s">
         <v>49</v>
@@ -3749,10 +3745,10 @@
         <v>90</v>
       </c>
       <c r="F72" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="G72" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J72" t="s">
         <v>102</v>
@@ -3778,7 +3774,7 @@
         <v>90</v>
       </c>
       <c r="F73" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G73" t="s">
         <v>49</v>
@@ -3807,7 +3803,7 @@
         <v>90</v>
       </c>
       <c r="F74" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="G74" t="s">
         <v>49</v>
@@ -3836,7 +3832,7 @@
         <v>90</v>
       </c>
       <c r="F75" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G75" t="s">
         <v>49</v>
@@ -3865,7 +3861,7 @@
         <v>90</v>
       </c>
       <c r="F76" t="s">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="G76" t="s">
         <v>49</v>
@@ -3894,7 +3890,7 @@
         <v>90</v>
       </c>
       <c r="F77" t="s">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="G77" t="s">
         <v>49</v>
@@ -3923,10 +3919,10 @@
         <v>90</v>
       </c>
       <c r="F78" t="s">
-        <v>93</v>
+        <v>254</v>
       </c>
       <c r="G78" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J78" t="s">
         <v>107</v>
@@ -3952,10 +3948,10 @@
         <v>90</v>
       </c>
       <c r="F79" t="s">
-        <v>91</v>
+        <v>286</v>
       </c>
       <c r="G79" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J79" t="s">
         <v>108</v>
@@ -3981,7 +3977,7 @@
         <v>90</v>
       </c>
       <c r="F80" t="s">
-        <v>98</v>
+        <v>285</v>
       </c>
       <c r="G80" t="s">
         <v>49</v>
@@ -4010,7 +4006,7 @@
         <v>90</v>
       </c>
       <c r="F81" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="G81" t="s">
         <v>49</v>
@@ -4039,7 +4035,7 @@
         <v>113</v>
       </c>
       <c r="F82" t="s">
-        <v>131</v>
+        <v>299</v>
       </c>
       <c r="G82" t="s">
         <v>49</v>
@@ -4074,7 +4070,7 @@
         <v>113</v>
       </c>
       <c r="F83" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G83" t="s">
         <v>49</v>
@@ -4109,7 +4105,7 @@
         <v>113</v>
       </c>
       <c r="F84" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G84" t="s">
         <v>49</v>
@@ -4144,7 +4140,7 @@
         <v>113</v>
       </c>
       <c r="F85" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="G85" t="s">
         <v>49</v>
@@ -4179,10 +4175,10 @@
         <v>113</v>
       </c>
       <c r="F86" t="s">
-        <v>229</v>
+        <v>302</v>
       </c>
       <c r="G86" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J86" t="s">
         <v>121</v>
@@ -4208,10 +4204,10 @@
         <v>113</v>
       </c>
       <c r="F87" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="G87" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J87" t="s">
         <v>123</v>
@@ -4237,7 +4233,7 @@
         <v>113</v>
       </c>
       <c r="F88" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G88" t="s">
         <v>49</v>
@@ -4266,10 +4262,10 @@
         <v>113</v>
       </c>
       <c r="F89" t="s">
-        <v>298</v>
+        <v>114</v>
       </c>
       <c r="G89" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J89" t="s">
         <v>125</v>
@@ -4295,10 +4291,10 @@
         <v>113</v>
       </c>
       <c r="F90" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="G90" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J90" t="s">
         <v>126</v>
@@ -4324,10 +4320,10 @@
         <v>113</v>
       </c>
       <c r="F91" t="s">
-        <v>300</v>
+        <v>131</v>
       </c>
       <c r="G91" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J91" t="s">
         <v>128</v>
@@ -4353,10 +4349,10 @@
         <v>113</v>
       </c>
       <c r="F92" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G92" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J92" t="s">
         <v>129</v>
@@ -4382,7 +4378,7 @@
         <v>113</v>
       </c>
       <c r="F93" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G93" t="s">
         <v>16</v>
@@ -4411,10 +4407,10 @@
         <v>113</v>
       </c>
       <c r="F94" t="s">
-        <v>303</v>
+        <v>229</v>
       </c>
       <c r="G94" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J94" t="s">
         <v>122</v>
@@ -4469,10 +4465,10 @@
         <v>113</v>
       </c>
       <c r="F96" t="s">
-        <v>114</v>
+        <v>300</v>
       </c>
       <c r="G96" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J96" t="s">
         <v>132</v>
@@ -4498,10 +4494,10 @@
         <v>113</v>
       </c>
       <c r="F97" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="G97" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J97" t="s">
         <v>133</v>
@@ -4527,7 +4523,7 @@
         <v>113</v>
       </c>
       <c r="F98" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="G98" t="s">
         <v>49</v>
@@ -4556,7 +4552,7 @@
         <v>113</v>
       </c>
       <c r="F99" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="G99" t="s">
         <v>49</v>
@@ -4585,7 +4581,7 @@
         <v>113</v>
       </c>
       <c r="F100" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="G100" t="s">
         <v>49</v>
@@ -4614,10 +4610,10 @@
         <v>113</v>
       </c>
       <c r="F101" t="s">
-        <v>307</v>
+        <v>266</v>
       </c>
       <c r="G101" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J101" t="s">
         <v>137</v>
@@ -4643,7 +4639,7 @@
         <v>141</v>
       </c>
       <c r="F102" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="G102" t="s">
         <v>49</v>
@@ -4678,7 +4674,7 @@
         <v>141</v>
       </c>
       <c r="F103" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="G103" t="s">
         <v>49</v>
@@ -4713,7 +4709,7 @@
         <v>141</v>
       </c>
       <c r="F104" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="G104" t="s">
         <v>49</v>
@@ -4748,7 +4744,7 @@
         <v>141</v>
       </c>
       <c r="F105" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="G105" t="s">
         <v>49</v>
@@ -4818,10 +4814,10 @@
         <v>141</v>
       </c>
       <c r="F107" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="G107" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J107" t="s">
         <v>148</v>
@@ -4876,7 +4872,7 @@
         <v>141</v>
       </c>
       <c r="F109" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="G109" t="s">
         <v>49</v>
@@ -4905,7 +4901,7 @@
         <v>141</v>
       </c>
       <c r="F110" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G110" t="s">
         <v>49</v>
@@ -4934,7 +4930,7 @@
         <v>141</v>
       </c>
       <c r="F111" t="s">
-        <v>183</v>
+        <v>308</v>
       </c>
       <c r="G111" t="s">
         <v>49</v>
@@ -4963,10 +4959,10 @@
         <v>141</v>
       </c>
       <c r="F112" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="G112" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J112" t="s">
         <v>40</v>
@@ -4992,10 +4988,10 @@
         <v>141</v>
       </c>
       <c r="F113" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G113" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J113" t="s">
         <v>152</v>
@@ -5021,7 +5017,7 @@
         <v>141</v>
       </c>
       <c r="F114" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G114" t="s">
         <v>49</v>
@@ -5050,10 +5046,10 @@
         <v>141</v>
       </c>
       <c r="F115" t="s">
-        <v>320</v>
+        <v>39</v>
       </c>
       <c r="G115" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J115" t="s">
         <v>143</v>
@@ -5079,7 +5075,7 @@
         <v>141</v>
       </c>
       <c r="F116" t="s">
-        <v>321</v>
+        <v>183</v>
       </c>
       <c r="G116" t="s">
         <v>49</v>
@@ -5108,7 +5104,7 @@
         <v>141</v>
       </c>
       <c r="F117" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G117" t="s">
         <v>49</v>
@@ -5137,7 +5133,7 @@
         <v>141</v>
       </c>
       <c r="F118" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="G118" t="s">
         <v>49</v>
@@ -5166,10 +5162,10 @@
         <v>141</v>
       </c>
       <c r="F119" t="s">
-        <v>147</v>
+        <v>318</v>
       </c>
       <c r="G119" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J119" t="s">
         <v>158</v>
@@ -5195,10 +5191,10 @@
         <v>141</v>
       </c>
       <c r="F120" t="s">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="G120" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J120" t="s">
         <v>159</v>
@@ -5224,10 +5220,10 @@
         <v>141</v>
       </c>
       <c r="F121" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="G121" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J121" t="s">
         <v>160</v>
@@ -5253,10 +5249,10 @@
         <v>163</v>
       </c>
       <c r="F122" t="s">
-        <v>325</v>
+        <v>164</v>
       </c>
       <c r="G122" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H122" t="s">
         <v>165</v>
@@ -5288,10 +5284,10 @@
         <v>163</v>
       </c>
       <c r="F123" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c r="G123" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H123" t="s">
         <v>164</v>
@@ -5323,10 +5319,10 @@
         <v>163</v>
       </c>
       <c r="F124" t="s">
-        <v>326</v>
+        <v>266</v>
       </c>
       <c r="G124" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J124" t="s">
         <v>73</v>
@@ -5352,7 +5348,7 @@
         <v>163</v>
       </c>
       <c r="F125" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="G125" t="s">
         <v>49</v>
@@ -5410,10 +5406,10 @@
         <v>163</v>
       </c>
       <c r="F127" t="s">
-        <v>329</v>
+        <v>175</v>
       </c>
       <c r="G127" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J127" t="s">
         <v>168</v>
@@ -5439,10 +5435,10 @@
         <v>163</v>
       </c>
       <c r="F128" t="s">
-        <v>330</v>
+        <v>52</v>
       </c>
       <c r="G128" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J128" t="s">
         <v>169</v>
@@ -5468,10 +5464,10 @@
         <v>163</v>
       </c>
       <c r="F129" t="s">
-        <v>168</v>
+        <v>333</v>
       </c>
       <c r="G129" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J129" t="s">
         <v>155</v>
@@ -5497,10 +5493,10 @@
         <v>163</v>
       </c>
       <c r="F130" t="s">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="G130" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J130" t="s">
         <v>170</v>
@@ -5526,10 +5522,10 @@
         <v>163</v>
       </c>
       <c r="F131" t="s">
-        <v>331</v>
+        <v>272</v>
       </c>
       <c r="G131" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J131" t="s">
         <v>171</v>
@@ -5555,10 +5551,10 @@
         <v>163</v>
       </c>
       <c r="F132" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="G132" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J132" t="s">
         <v>21</v>
@@ -5584,10 +5580,10 @@
         <v>163</v>
       </c>
       <c r="F133" t="s">
-        <v>332</v>
+        <v>168</v>
       </c>
       <c r="G133" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J133" t="s">
         <v>52</v>
@@ -5613,7 +5609,7 @@
         <v>163</v>
       </c>
       <c r="F134" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="G134" t="s">
         <v>49</v>
@@ -5642,10 +5638,10 @@
         <v>163</v>
       </c>
       <c r="F135" t="s">
-        <v>52</v>
+        <v>332</v>
       </c>
       <c r="G135" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J135" t="s">
         <v>173</v>
@@ -5671,10 +5667,10 @@
         <v>163</v>
       </c>
       <c r="F136" t="s">
-        <v>164</v>
+        <v>329</v>
       </c>
       <c r="G136" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J136" t="s">
         <v>149</v>
@@ -5700,7 +5696,7 @@
         <v>163</v>
       </c>
       <c r="F137" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G137" t="s">
         <v>49</v>
@@ -5729,10 +5725,10 @@
         <v>163</v>
       </c>
       <c r="F138" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G138" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J138" t="s">
         <v>175</v>
@@ -5758,10 +5754,10 @@
         <v>163</v>
       </c>
       <c r="F139" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="G139" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J139" t="s">
         <v>176</v>
@@ -5787,10 +5783,10 @@
         <v>163</v>
       </c>
       <c r="F140" t="s">
-        <v>175</v>
+        <v>326</v>
       </c>
       <c r="G140" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J140" t="s">
         <v>177</v>
@@ -5845,7 +5841,7 @@
         <v>182</v>
       </c>
       <c r="F142" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="G142" t="s">
         <v>49</v>
@@ -5880,10 +5876,10 @@
         <v>182</v>
       </c>
       <c r="F143" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="G143" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H143" t="s">
         <v>185</v>
@@ -5915,7 +5911,7 @@
         <v>182</v>
       </c>
       <c r="F144" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="G144" t="s">
         <v>49</v>
@@ -5950,7 +5946,7 @@
         <v>182</v>
       </c>
       <c r="F145" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G145" t="s">
         <v>49</v>
@@ -5985,7 +5981,7 @@
         <v>182</v>
       </c>
       <c r="F146" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G146" t="s">
         <v>49</v>
@@ -6020,7 +6016,7 @@
         <v>182</v>
       </c>
       <c r="F147" t="s">
-        <v>342</v>
+        <v>191</v>
       </c>
       <c r="G147" t="s">
         <v>49</v>
@@ -6049,10 +6045,10 @@
         <v>182</v>
       </c>
       <c r="F148" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="G148" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J148" t="s">
         <v>189</v>
@@ -6078,7 +6074,7 @@
         <v>182</v>
       </c>
       <c r="F149" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G149" t="s">
         <v>49</v>
@@ -6107,7 +6103,7 @@
         <v>182</v>
       </c>
       <c r="F150" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G150" t="s">
         <v>49</v>
@@ -6165,7 +6161,7 @@
         <v>182</v>
       </c>
       <c r="F152" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G152" t="s">
         <v>49</v>
@@ -6194,10 +6190,10 @@
         <v>182</v>
       </c>
       <c r="F153" t="s">
-        <v>348</v>
+        <v>198</v>
       </c>
       <c r="G153" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J153" t="s">
         <v>194</v>
@@ -6223,7 +6219,7 @@
         <v>182</v>
       </c>
       <c r="F154" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="G154" t="s">
         <v>49</v>
@@ -6252,7 +6248,7 @@
         <v>182</v>
       </c>
       <c r="F155" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G155" t="s">
         <v>49</v>
@@ -6281,7 +6277,7 @@
         <v>182</v>
       </c>
       <c r="F156" t="s">
-        <v>191</v>
+        <v>341</v>
       </c>
       <c r="G156" t="s">
         <v>49</v>
@@ -6310,10 +6306,10 @@
         <v>182</v>
       </c>
       <c r="F157" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G157" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J157" t="s">
         <v>198</v>
@@ -6339,10 +6335,10 @@
         <v>182</v>
       </c>
       <c r="F158" t="s">
-        <v>198</v>
+        <v>348</v>
       </c>
       <c r="G158" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J158" t="s">
         <v>199</v>
@@ -6368,7 +6364,7 @@
         <v>182</v>
       </c>
       <c r="F159" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="G159" t="s">
         <v>49</v>
@@ -6397,10 +6393,10 @@
         <v>182</v>
       </c>
       <c r="F160" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="G160" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J160" t="s">
         <v>200</v>
@@ -6426,7 +6422,7 @@
         <v>182</v>
       </c>
       <c r="F161" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="G161" t="s">
         <v>49</v>
@@ -6455,7 +6451,7 @@
         <v>11</v>
       </c>
       <c r="F162" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="G162" t="s">
         <v>49</v>
@@ -6490,10 +6486,10 @@
         <v>11</v>
       </c>
       <c r="F163" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="G163" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H163" t="s">
         <v>206</v>
@@ -6525,10 +6521,10 @@
         <v>11</v>
       </c>
       <c r="F164" t="s">
-        <v>357</v>
+        <v>211</v>
       </c>
       <c r="G164" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H164" t="s">
         <v>208</v>
@@ -6560,10 +6556,10 @@
         <v>11</v>
       </c>
       <c r="F165" t="s">
-        <v>358</v>
+        <v>206</v>
       </c>
       <c r="G165" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H165" t="s">
         <v>203</v>
@@ -6595,7 +6591,7 @@
         <v>11</v>
       </c>
       <c r="F166" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="G166" t="s">
         <v>49</v>
@@ -6624,10 +6620,10 @@
         <v>11</v>
       </c>
       <c r="F167" t="s">
-        <v>360</v>
+        <v>218</v>
       </c>
       <c r="G167" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J167" t="s">
         <v>211</v>
@@ -6653,7 +6649,7 @@
         <v>11</v>
       </c>
       <c r="F168" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G168" t="s">
         <v>49</v>
@@ -6682,7 +6678,7 @@
         <v>11</v>
       </c>
       <c r="F169" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G169" t="s">
         <v>49</v>
@@ -6711,10 +6707,10 @@
         <v>11</v>
       </c>
       <c r="F170" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="G170" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J170" t="s">
         <v>214</v>
@@ -6740,10 +6736,10 @@
         <v>11</v>
       </c>
       <c r="F171" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G171" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J171" t="s">
         <v>215</v>
@@ -6769,10 +6765,10 @@
         <v>11</v>
       </c>
       <c r="F172" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G172" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J172" t="s">
         <v>206</v>
@@ -6798,10 +6794,10 @@
         <v>11</v>
       </c>
       <c r="F173" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G173" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J173" t="s">
         <v>216</v>
@@ -6856,10 +6852,10 @@
         <v>11</v>
       </c>
       <c r="F175" t="s">
-        <v>208</v>
+        <v>358</v>
       </c>
       <c r="G175" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J175" t="s">
         <v>218</v>
@@ -6885,10 +6881,10 @@
         <v>11</v>
       </c>
       <c r="F176" t="s">
-        <v>211</v>
+        <v>359</v>
       </c>
       <c r="G176" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J176" t="s">
         <v>219</v>
@@ -6914,10 +6910,10 @@
         <v>11</v>
       </c>
       <c r="F177" t="s">
-        <v>203</v>
+        <v>365</v>
       </c>
       <c r="G177" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J177" t="s">
         <v>220</v>
@@ -6943,7 +6939,7 @@
         <v>11</v>
       </c>
       <c r="F178" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="G178" t="s">
         <v>49</v>
@@ -6972,7 +6968,7 @@
         <v>11</v>
       </c>
       <c r="F179" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="G179" t="s">
         <v>49</v>
@@ -7001,10 +6997,10 @@
         <v>11</v>
       </c>
       <c r="F180" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G180" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J180" t="s">
         <v>45</v>
@@ -7030,7 +7026,7 @@
         <v>11</v>
       </c>
       <c r="F181" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="G181" t="s">
         <v>13</v>
@@ -7059,10 +7055,10 @@
         <v>11</v>
       </c>
       <c r="F182" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="G182" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="H182" t="s">
         <v>226</v>
@@ -7094,7 +7090,7 @@
         <v>11</v>
       </c>
       <c r="F183" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="G183" t="s">
         <v>49</v>
@@ -7129,7 +7125,7 @@
         <v>11</v>
       </c>
       <c r="F184" t="s">
-        <v>372</v>
+        <v>268</v>
       </c>
       <c r="G184" t="s">
         <v>49</v>
@@ -7164,7 +7160,7 @@
         <v>11</v>
       </c>
       <c r="F185" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G185" t="s">
         <v>49</v>
@@ -7199,7 +7195,7 @@
         <v>11</v>
       </c>
       <c r="F186" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G186" t="s">
         <v>49</v>
@@ -7234,7 +7230,7 @@
         <v>11</v>
       </c>
       <c r="F187" t="s">
-        <v>52</v>
+        <v>385</v>
       </c>
       <c r="G187" t="s">
         <v>49</v>
@@ -7263,7 +7259,7 @@
         <v>11</v>
       </c>
       <c r="F188" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G188" t="s">
         <v>49</v>
@@ -7292,7 +7288,7 @@
         <v>11</v>
       </c>
       <c r="F189" t="s">
-        <v>268</v>
+        <v>381</v>
       </c>
       <c r="G189" t="s">
         <v>49</v>
@@ -7321,10 +7317,10 @@
         <v>11</v>
       </c>
       <c r="F190" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="G190" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="J190" t="s">
         <v>236</v>
@@ -7350,7 +7346,7 @@
         <v>11</v>
       </c>
       <c r="F191" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G191" t="s">
         <v>49</v>
@@ -7379,7 +7375,7 @@
         <v>11</v>
       </c>
       <c r="F192" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G192" t="s">
         <v>49</v>
@@ -7408,10 +7404,10 @@
         <v>11</v>
       </c>
       <c r="F193" t="s">
-        <v>379</v>
+        <v>243</v>
       </c>
       <c r="G193" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="J193" t="s">
         <v>238</v>
@@ -7437,7 +7433,7 @@
         <v>11</v>
       </c>
       <c r="F194" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="G194" t="s">
         <v>49</v>
@@ -7466,7 +7462,7 @@
         <v>11</v>
       </c>
       <c r="F195" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="G195" t="s">
         <v>49</v>
@@ -7495,7 +7491,7 @@
         <v>11</v>
       </c>
       <c r="F196" t="s">
-        <v>228</v>
+        <v>382</v>
       </c>
       <c r="G196" t="s">
         <v>16</v>
@@ -7524,10 +7520,10 @@
         <v>11</v>
       </c>
       <c r="F197" t="s">
-        <v>382</v>
+        <v>52</v>
       </c>
       <c r="G197" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J197" t="s">
         <v>241</v>
@@ -7553,10 +7549,10 @@
         <v>11</v>
       </c>
       <c r="F198" t="s">
-        <v>243</v>
+        <v>370</v>
       </c>
       <c r="G198" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J198" t="s">
         <v>242</v>
@@ -7582,7 +7578,7 @@
         <v>11</v>
       </c>
       <c r="F199" t="s">
-        <v>383</v>
+        <v>228</v>
       </c>
       <c r="G199" t="s">
         <v>16</v>
@@ -7611,10 +7607,10 @@
         <v>11</v>
       </c>
       <c r="F200" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="G200" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="J200" t="s">
         <v>244</v>
@@ -7640,7 +7636,7 @@
         <v>11</v>
       </c>
       <c r="F201" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="G201" t="s">
         <v>49</v>
